--- a/temp.xlsx
+++ b/temp.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{199AA67A-A22B-4734-A418-9DB3E02B855D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-37845" yWindow="-7365" windowWidth="19410" windowHeight="20985" xr2:uid="{551E7064-0386-4203-BD17-B05DA195E3BD}"/>
+    <workbookView xWindow="-21645" yWindow="-2775" windowWidth="19410" windowHeight="20985" xr2:uid="{551E7064-0386-4203-BD17-B05DA195E3BD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -284,7 +284,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -295,7 +295,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -670,15 +669,14 @@
   <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.85546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="4"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
@@ -708,92 +706,92 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="5">
         <v>27</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="5">
         <v>76</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="5">
         <v>272</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="5">
         <v>164</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2" s="6">
         <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="8">
         <v>30.9</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="8">
         <v>65</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="8">
         <v>222</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="8">
         <v>191</v>
       </c>
-      <c r="H3" s="10">
+      <c r="H3" s="9">
         <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="11">
         <v>32.299999999999997</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="11">
         <v>63</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="11">
         <v>114</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="11">
         <v>318</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="12">
         <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="11"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="13"/>
+      <c r="A5" s="10"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="12"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -824,80 +822,80 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="5">
         <v>46.6</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="5">
         <v>27</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="13">
         <v>1106</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="5">
         <v>14</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H9" s="6">
         <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="8">
         <v>41.1</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="8">
         <v>35</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="15">
         <v>1918</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="8">
         <v>8</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="9">
         <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="11">
         <v>39.5</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="11">
         <v>38</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="11">
         <v>407</v>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="11">
         <v>104</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="12">
         <v>31</v>
       </c>
     </row>
